--- a/WorkBot/refactor-experimental/data/orders/Peters Supply/Peters Supply_Syracuse_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Peters Supply/Peters Supply_Syracuse_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Glove Nitrile - XLarge</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>105.00</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E2" t="n">
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Glove Nitrile - Med</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>52.5</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Glove Nitrile - Large</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>52.50</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>52.5</v>
       </c>
     </row>
   </sheetData>
